--- a/data/trans_dic/P55$nadie-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P55$nadie-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,46</t>
+          <t>0,0; 43,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,7</t>
+          <t>0,0; 48,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,8</t>
+          <t>0,0; 14,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,38</t>
+          <t>0,0; 15,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,6</t>
+          <t>0,0; 15,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,11</t>
+          <t>0,0; 14,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,02</t>
+          <t>0,0; 17,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,25</t>
+          <t>0,0; 6,05</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,71</t>
+          <t>0,0; 39,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,33</t>
+          <t>0,0; 48,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,52</t>
+          <t>0,0; 24,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,61</t>
+          <t>0,0; 7,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,66</t>
+          <t>0,0; 22,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,24</t>
+          <t>0,0; 18,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,83</t>
+          <t>0,0; 5,68</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 22,98</t>
+          <t>4,07; 22,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,59</t>
+          <t>0,0; 13,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,03</t>
+          <t>0,0; 30,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 15,7</t>
+          <t>2,66; 14,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,27</t>
+          <t>0,0; 11,59</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,43</t>
+          <t>0,0; 18,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 15,0</t>
+          <t>4,58; 14,68</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 27,76</t>
+          <t>3,37; 29,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,0</t>
+          <t>0,0; 13,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,67</t>
+          <t>0,0; 21,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,77</t>
+          <t>0,0; 5,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 21,15</t>
+          <t>2,37; 20,02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,71</t>
+          <t>0,0; 8,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,8</t>
+          <t>0,0; 14,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>0,0; 3,26</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,55; 44,11</t>
+          <t>3,99; 41,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,54</t>
+          <t>0,0; 14,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 35,53</t>
+          <t>3,33; 36,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,13</t>
+          <t>0,0; 10,32</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,37; 14,38</t>
+          <t>1,37; 15,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,12</t>
+          <t>0,0; 23,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,17; 43,27</t>
+          <t>5,18; 42,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,69; 16,79</t>
+          <t>3,71; 16,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,04</t>
+          <t>0,0; 14,42</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,38; 28,23</t>
+          <t>3,48; 29,29</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,68; 13,34</t>
+          <t>3,54; 13,05</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,35; 33,88</t>
+          <t>4,42; 35,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,47</t>
+          <t>0,0; 16,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,39</t>
+          <t>0,0; 16,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,97; 26,96</t>
+          <t>2,99; 26,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,89</t>
+          <t>0,0; 16,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,72</t>
+          <t>0,0; 11,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 17,68</t>
+          <t>2,01; 19,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,37; 13,26</t>
+          <t>2,67; 13,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,1; 17,85</t>
+          <t>2,92; 17,54</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,51</t>
+          <t>0,0; 8,5</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 14,67</t>
+          <t>2,59; 13,79</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 13,53</t>
+          <t>3,73; 13,16</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,66</t>
+          <t>0,0; 19,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,66</t>
+          <t>0,0; 22,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,09</t>
+          <t>0,0; 22,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,55; 22,03</t>
+          <t>3,8; 23,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,29; 19,44</t>
+          <t>2,31; 21,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,36; 18,83</t>
+          <t>2,42; 20,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,81; 9,32</t>
+          <t>1,81; 10,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,95; 16,84</t>
+          <t>3,5; 16,05</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,62; 15,2</t>
+          <t>1,72; 15,15</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,68; 14,34</t>
+          <t>1,65; 13,98</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,24; 10,83</t>
+          <t>2,17; 10,07</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,18; 10,48</t>
+          <t>2,15; 10,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,4; 10,18</t>
+          <t>1,4; 11,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,35</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,07; 8,75</t>
+          <t>3,01; 8,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,88; 10,35</t>
+          <t>3,71; 10,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,47</t>
+          <t>0,8; 4,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,07; 12,54</t>
+          <t>5,28; 12,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,43</t>
+          <t>3,12; 6,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,85; 9,5</t>
+          <t>3,77; 8,9</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,28</t>
+          <t>1,51; 5,38</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4,04; 9,55</t>
+          <t>3,82; 9,1</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,56; 6,46</t>
+          <t>3,31; 6,26</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1624</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4884</t>
+          <t>0; 5120</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3392</t>
+          <t>0; 4362</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3730</t>
+          <t>0; 3821</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1919</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4942</t>
+          <t>0; 4341</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5596</t>
+          <t>0; 3877</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 940</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1889</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 6881</t>
+          <t>0; 5989</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5746</t>
+          <t>0; 5902</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4347</t>
+          <t>0; 3627</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6465</t>
+          <t>0; 6455</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 9720</t>
+          <t>0; 11386</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1605</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1536</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4659</t>
+          <t>0; 5635</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2073</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2389</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4734</t>
+          <t>0; 4180</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 9225</t>
+          <t>0; 8923</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 12672</t>
+          <t>0; 12217</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2181</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 4103</t>
+          <t>0; 4001</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1634</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1942</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1472</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1097; 5902</t>
+          <t>1044; 5876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4859</t>
+          <t>0; 4875</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1940</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5551</t>
+          <t>0; 5198</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1206; 6992</t>
+          <t>1184; 6564</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5203</t>
+          <t>0; 5350</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 2003</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4947</t>
+          <t>0; 5898</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3421; 10532</t>
+          <t>3215; 10304</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1688</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1924</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1556</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1126</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1068; 8860</t>
+          <t>1077; 9312</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5130</t>
+          <t>0; 5196</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6368</t>
+          <t>0; 6424</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2434</t>
+          <t>0; 2036</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1106; 9583</t>
+          <t>1073; 9069</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5116</t>
+          <t>0; 5139</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 6413</t>
+          <t>0; 6497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 1673</t>
+          <t>0; 1710</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1355</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1862</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1303</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 891</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1848</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1923</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1099; 10657</t>
+          <t>964; 10098</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2669</t>
+          <t>0; 2304</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 1711</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 1979</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>999; 10335</t>
+          <t>970; 10556</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2685</t>
+          <t>0; 2491</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1706</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1905</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1492</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>332; 3477</t>
+          <t>331; 3697</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6742</t>
+          <t>0; 6531</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1210; 10121</t>
+          <t>1212; 9954</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1166; 5301</t>
+          <t>1170; 5351</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6907</t>
+          <t>0; 6622</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 1978</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1295; 10817</t>
+          <t>1335; 11226</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2050; 7440</t>
+          <t>1975; 7277</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>813; 6340</t>
+          <t>828; 6589</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5123</t>
+          <t>0; 4740</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5126</t>
+          <t>0; 4313</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>691; 6267</t>
+          <t>696; 6159</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 7009</t>
+          <t>0; 6514</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 4801</t>
+          <t>0; 5789</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1104; 9960</t>
+          <t>1131; 10984</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1264; 7083</t>
+          <t>1428; 6984</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1796; 10333</t>
+          <t>1690; 10153</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 6700</t>
+          <t>0; 6692</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2164; 12137</t>
+          <t>2143; 11416</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2877; 10374</t>
+          <t>2862; 10089</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 6064</t>
+          <t>0; 6181</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 5761</t>
+          <t>0; 4595</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 1745</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 3926</t>
+          <t>0; 3842</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1690; 10479</t>
+          <t>1808; 11053</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1073; 9114</t>
+          <t>1083; 9975</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1314; 10484</t>
+          <t>1347; 11342</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1064; 5475</t>
+          <t>1062; 5950</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3159; 13483</t>
+          <t>2802; 12852</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1094; 10295</t>
+          <t>1165; 10256</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1349; 11529</t>
+          <t>1328; 11244</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1697; 8204</t>
+          <t>1646; 7629</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2765; 13269</t>
+          <t>2724; 13387</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2039; 14879</t>
+          <t>2040; 16193</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 6503</t>
+          <t>0; 6573</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4824; 13738</t>
+          <t>4722; 14007</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>8948; 23910</t>
+          <t>8557; 23850</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2341; 12494</t>
+          <t>2238; 13353</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13564; 33523</t>
+          <t>14120; 33383</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>10260; 21099</t>
+          <t>10249; 19982</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>13766; 33965</t>
+          <t>13473; 31810</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7058; 22497</t>
+          <t>6426; 22914</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15700; 37119</t>
+          <t>14844; 35393</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>17267; 31358</t>
+          <t>16054; 30365</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$nadie-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P55$nadie-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,47</t>
+          <t>0,0; 39,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,47</t>
+          <t>0,0; 35,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,13</t>
+          <t>0,0; 15,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,12 +742,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,26</t>
+          <t>0,0; 19,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,66</t>
+          <t>0,0; 17,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,89</t>
+          <t>0,0; 15,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,48</t>
+          <t>0,0; 16,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,05</t>
+          <t>0,0; 6,49</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,65</t>
+          <t>0,0; 47,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,42</t>
+          <t>0,0; 38,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,81</t>
+          <t>0,0; 20,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -892,17 +892,17 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,6</t>
+          <t>0,0; 7,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,89</t>
+          <t>0,0; 22,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,55</t>
+          <t>0,0; 20,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,68</t>
+          <t>0,0; 5,94</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 22,88</t>
+          <t>4,57; 23,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,64</t>
+          <t>0,0; 16,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,17 +1027,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,0</t>
+          <t>0,0; 28,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 14,74</t>
+          <t>2,71; 15,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,59</t>
+          <t>0,0; 8,32</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,39</t>
+          <t>0,0; 18,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 14,68</t>
+          <t>4,85; 15,36</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1157,42 +1157,42 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 29,17</t>
+          <t>3,4; 27,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,17</t>
+          <t>0,0; 13,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,87</t>
+          <t>0,0; 25,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,67</t>
+          <t>0,0; 5,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 20,02</t>
+          <t>2,38; 20,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,75</t>
+          <t>0,0; 9,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,99</t>
+          <t>0,0; 14,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,26</t>
+          <t>0,0; 4,37</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,99; 41,8</t>
+          <t>4,07; 45,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,28</t>
+          <t>0,0; 14,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1327,12 +1327,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 36,29</t>
+          <t>3,23; 34,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,32</t>
+          <t>0,0; 11,16</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,37; 15,29</t>
+          <t>1,38; 14,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,36</t>
+          <t>0,0; 24,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,18; 42,56</t>
+          <t>5,23; 43,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,71; 16,95</t>
+          <t>3,77; 16,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,42</t>
+          <t>0,0; 15,99</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,48; 29,29</t>
+          <t>3,22; 29,88</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,54; 13,05</t>
+          <t>3,61; 12,59</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,42; 35,21</t>
+          <t>4,45; 35,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,16</t>
+          <t>0,0; 15,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,32</t>
+          <t>0,0; 21,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 26,5</t>
+          <t>3,11; 24,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,63</t>
+          <t>0,0; 16,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,73</t>
+          <t>0,0; 10,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 19,5</t>
+          <t>1,96; 16,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 13,07</t>
+          <t>3,07; 13,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,92; 17,54</t>
+          <t>2,92; 17,55</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,5</t>
+          <t>0,0; 8,02</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 13,79</t>
+          <t>2,58; 13,41</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,73; 13,16</t>
+          <t>3,97; 14,03</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,02</t>
+          <t>0,0; 18,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,06</t>
+          <t>0,0; 27,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1712,47 +1712,47 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,6</t>
+          <t>0,0; 24,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,8; 23,24</t>
+          <t>3,82; 21,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,31; 21,27</t>
+          <t>2,29; 17,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,42; 20,37</t>
+          <t>2,32; 19,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,81; 10,13</t>
+          <t>1,74; 9,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,5; 16,05</t>
+          <t>4,08; 16,17</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,72; 15,15</t>
+          <t>1,6; 14,91</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,65; 13,98</t>
+          <t>1,65; 13,6</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,17; 10,07</t>
+          <t>2,11; 9,34</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,15; 10,58</t>
+          <t>2,12; 11,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,4; 11,08</t>
+          <t>1,36; 10,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,0; 4,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,01; 8,92</t>
+          <t>3,06; 8,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,71; 10,33</t>
+          <t>3,67; 10,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,78</t>
+          <t>0,82; 4,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,28; 12,49</t>
+          <t>5,32; 12,65</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,09</t>
+          <t>3,04; 6,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,77; 8,9</t>
+          <t>3,95; 9,15</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,38</t>
+          <t>1,52; 5,41</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,82; 9,1</t>
+          <t>4,0; 9,27</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,26</t>
+          <t>3,61; 6,53</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>752</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>752</t>
         </is>
       </c>
     </row>
@@ -2214,17 +2214,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5120</t>
+          <t>0; 4640</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4362</t>
+          <t>0; 3227</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3821</t>
+          <t>0; 4468</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4341</t>
+          <t>0; 5511</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3877</t>
+          <t>0; 4247</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2254,17 +2254,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5989</t>
+          <t>0; 6037</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5902</t>
+          <t>0; 5551</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3627</t>
+          <t>0; 4078</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1224</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6455</t>
+          <t>0; 7691</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 11386</t>
+          <t>0; 9109</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5635</t>
+          <t>0; 4703</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2452,17 +2452,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4180</t>
+          <t>0; 4323</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 8923</t>
+          <t>0; 8833</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 12217</t>
+          <t>0; 13369</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 4001</t>
+          <t>0; 4451</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6287</t>
         </is>
       </c>
     </row>
@@ -2640,12 +2640,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1044; 5876</t>
+          <t>1154; 5956</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4875</t>
+          <t>0; 5844</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2655,17 +2655,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5198</t>
+          <t>0; 4901</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1184; 6564</t>
+          <t>1210; 6727</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5350</t>
+          <t>0; 3840</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -2675,12 +2675,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 5898</t>
+          <t>0; 6013</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3215; 10304</t>
+          <t>3384; 10728</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
     </row>
@@ -2853,42 +2853,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1077; 9312</t>
+          <t>1084; 8881</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5196</t>
+          <t>0; 5187</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6424</t>
+          <t>0; 7454</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2036</t>
+          <t>0; 2171</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1073; 9069</t>
+          <t>1076; 9359</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5139</t>
+          <t>0; 5544</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 6497</t>
+          <t>0; 6307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 1710</t>
+          <t>0; 2439</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>781</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>781</t>
         </is>
       </c>
     </row>
@@ -3071,12 +3071,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>964; 10098</t>
+          <t>984; 10969</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2304</t>
+          <t>0; 2398</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>970; 10556</t>
+          <t>941; 10173</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2491</t>
+          <t>0; 2789</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4140</t>
         </is>
       </c>
     </row>
@@ -3264,12 +3264,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>331; 3697</t>
+          <t>333; 3442</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6531</t>
+          <t>0; 6942</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3279,17 +3279,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1212; 9954</t>
+          <t>1223; 10253</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1170; 5351</t>
+          <t>1212; 5320</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6622</t>
+          <t>0; 7341</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1335; 11226</t>
+          <t>1233; 11452</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1975; 7277</t>
+          <t>2034; 7098</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>7409</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>828; 6589</t>
+          <t>832; 6576</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4740</t>
+          <t>0; 4539</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4313</t>
+          <t>0; 5728</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>696; 6159</t>
+          <t>890; 7085</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 6514</t>
+          <t>0; 6379</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 5789</t>
+          <t>0; 5409</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1131; 10984</t>
+          <t>1106; 9304</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1428; 6984</t>
+          <t>2001; 8945</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1690; 10153</t>
+          <t>1689; 10161</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 6692</t>
+          <t>0; 6314</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2143; 11416</t>
+          <t>2136; 11094</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2862; 10089</t>
+          <t>3729; 13173</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>4393</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 6181</t>
+          <t>0; 5900</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 4595</t>
+          <t>0; 5788</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3680,47 +3680,47 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 3842</t>
+          <t>0; 4699</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1808; 11053</t>
+          <t>1817; 10065</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1083; 9975</t>
+          <t>1076; 8115</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1347; 11342</t>
+          <t>1293; 11006</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1062; 5950</t>
+          <t>1186; 6665</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2802; 12852</t>
+          <t>3266; 12948</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1165; 10256</t>
+          <t>1083; 10093</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1328; 11244</t>
+          <t>1328; 10938</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1646; 7629</t>
+          <t>1855; 8198</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>14724</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>23124</t>
+          <t>25416</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2724; 13387</t>
+          <t>2680; 14318</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2040; 16193</t>
+          <t>1985; 15764</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 6573</t>
+          <t>0; 5968</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4722; 14007</t>
+          <t>5172; 14989</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>8557; 23850</t>
+          <t>8471; 23526</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2238; 13353</t>
+          <t>2280; 13169</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14120; 33383</t>
+          <t>14223; 33820</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>10249; 19982</t>
+          <t>10871; 23262</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>13473; 31810</t>
+          <t>14130; 32718</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6426; 22914</t>
+          <t>6480; 23012</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14844; 35393</t>
+          <t>15546; 36057</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>16054; 30365</t>
+          <t>19009; 34345</t>
         </is>
       </c>
     </row>
